--- a/etf_holdings/2026-10-20_common_daily_changes_summary.xlsx
+++ b/etf_holdings/2026-10-20_common_daily_changes_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -469,7 +469,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>00991A(12,000)、00403A(15,000)、00400A(20,000)</t>
+          <t>00403A(15,000)、00400A(20,000)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -481,16 +481,16 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -499,7 +499,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>00981A(40,000)、00982A(2,000)、00403A(60,000)</t>
+          <t>00985A(25,000)、00400A(148,000)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -511,12 +511,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -524,225 +524,15 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>00982A(37,000)</t>
+          <t>00403A(153,000)、00985A(165,000)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
-        <is>
-          <t>00403A(-5,000,000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>台積電</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>全部加碼</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>00981A(279,000)、00400A(37,000)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>智邦</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>全部加碼</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>00985A(25,000)、00400A(148,000)</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2449</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>京元電子</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>混合</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>00981A(1,200,000)</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>00990A(全數賣出)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2454</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>聯發科</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>全部加碼</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>00982A(50,000)、00400A(69,000)</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>3008</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>大立光</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>2</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>全部加碼</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>00991A(20,000)、00982A(2,000)</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>3231</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>緯創</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>2</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>全部加碼</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>00981A(新納入)、00407A(320,000)</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>6669</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>緯穎</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>全部加碼</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>00403A(153,000)、00985A(165,000)</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/etf_holdings/2026-10-20_common_daily_changes_summary.xlsx
+++ b/etf_holdings/2026-10-20_common_daily_changes_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,42 +451,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>全部加碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>00403A(15,000)、00400A(20,000)</t>
+          <t>00981A(新納入)、00407A(320,000)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00992A(-2,731,000)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -499,7 +499,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>00985A(25,000)、00400A(148,000)</t>
+          <t>00991A(12,000)、00400A(20,000)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -511,12 +511,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -529,10 +529,190 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>00403A(153,000)、00985A(165,000)</t>
+          <t>00981A(279,000)、00400A(37,000)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>00985A(25,000)、00400A(148,000)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2383</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>00985A(2,000)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>00992A(-55,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2449</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>混合</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>00981A(1,200,000)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>00990A(全數賣出)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>00982A(50,000)、00400A(69,000)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>00991A(20,000)、00982A(2,000)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>00981A(40,000)、00982A(2,000)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
